--- a/artfynd/A 64809-2023 artfynd.xlsx
+++ b/artfynd/A 64809-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY92"/>
+  <dimension ref="A1:AY101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1227,32 +1227,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135331130</v>
+        <v>135331133</v>
       </c>
       <c r="B7" t="n">
-        <v>79442</v>
+        <v>92245</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>639</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grenlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Evernia mesomorpha</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1262,13 +1262,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623561</v>
+        <v>623534</v>
       </c>
       <c r="R7" t="n">
-        <v>7307299</v>
+        <v>7307322</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1338,7 +1338,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135331133</v>
+        <v>135331136</v>
       </c>
       <c r="B8" t="n">
         <v>92245</v>
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623534</v>
+        <v>623564</v>
       </c>
       <c r="R8" t="n">
-        <v>7307322</v>
+        <v>7307337</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,7 +1449,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135331136</v>
+        <v>135333192</v>
       </c>
       <c r="B9" t="n">
         <v>92245</v>
@@ -1480,17 +1480,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623564</v>
+        <v>623498</v>
       </c>
       <c r="R9" t="n">
-        <v>7307337</v>
+        <v>7307367</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1544,12 +1544,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1560,10 +1560,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135333192</v>
+        <v>135333369</v>
       </c>
       <c r="B10" t="n">
-        <v>92245</v>
+        <v>79452</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,37 +1571,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>864</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>623498</v>
+        <v>624013</v>
       </c>
       <c r="R10" t="n">
-        <v>7307367</v>
+        <v>7307360</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1655,12 +1655,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1671,48 +1671,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135333369</v>
+        <v>135333193</v>
       </c>
       <c r="B11" t="n">
-        <v>79452</v>
+        <v>92795</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>864</v>
+        <v>918</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>624013</v>
+        <v>623559</v>
       </c>
       <c r="R11" t="n">
-        <v>7307360</v>
+        <v>7307431</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1766,12 +1766,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1782,7 +1782,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135333193</v>
+        <v>135333379</v>
       </c>
       <c r="B12" t="n">
         <v>92795</v>
@@ -1813,17 +1813,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>623559</v>
+        <v>624069</v>
       </c>
       <c r="R12" t="n">
-        <v>7307431</v>
+        <v>7307333</v>
       </c>
       <c r="S12" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1877,12 +1877,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1893,7 +1893,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135333379</v>
+        <v>135337856</v>
       </c>
       <c r="B13" t="n">
         <v>92795</v>
@@ -1924,14 +1924,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>624069</v>
+        <v>623566</v>
       </c>
       <c r="R13" t="n">
-        <v>7307333</v>
+        <v>7307479</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1973,7 +1973,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På gran rörligt markvatten. Har kollekt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1982,18 +1987,19 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2317,10 +2323,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135331028</v>
+        <v>135337861</v>
       </c>
       <c r="B17" t="n">
-        <v>83222</v>
+        <v>91974</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2328,37 +2334,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nära Änganäs, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>623662</v>
+        <v>623609</v>
       </c>
       <c r="R17" t="n">
-        <v>7307297</v>
+        <v>7307443</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2385,29 +2391,45 @@
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På tall över fuktigt vatten</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2418,7 +2440,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135331037</v>
+        <v>135331028</v>
       </c>
       <c r="B18" t="n">
         <v>83222</v>
@@ -2453,13 +2475,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>623600</v>
+        <v>623662</v>
       </c>
       <c r="R18" t="n">
-        <v>7307269</v>
+        <v>7307297</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2519,7 +2541,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135331141</v>
+        <v>135331037</v>
       </c>
       <c r="B19" t="n">
         <v>83222</v>
@@ -2550,17 +2572,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Nära Änganäs, Pi lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>623557</v>
+        <v>623600</v>
       </c>
       <c r="R19" t="n">
-        <v>7307476</v>
+        <v>7307269</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2587,19 +2609,9 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>16:01</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>16:01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2614,12 +2626,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2630,7 +2642,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135332774</v>
+        <v>135331141</v>
       </c>
       <c r="B20" t="n">
         <v>83222</v>
@@ -2661,17 +2673,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>623973</v>
+        <v>623557</v>
       </c>
       <c r="R20" t="n">
-        <v>7307330</v>
+        <v>7307476</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2700,7 +2712,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2710,7 +2722,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2725,12 +2737,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2741,7 +2753,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135333363</v>
+        <v>135332774</v>
       </c>
       <c r="B21" t="n">
         <v>83222</v>
@@ -2776,13 +2788,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>624035</v>
+        <v>623973</v>
       </c>
       <c r="R21" t="n">
-        <v>7307280</v>
+        <v>7307330</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2811,7 +2823,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2821,7 +2833,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2836,12 +2848,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2852,7 +2864,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135333367</v>
+        <v>135333363</v>
       </c>
       <c r="B22" t="n">
         <v>83222</v>
@@ -2887,13 +2899,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>624036</v>
+        <v>624035</v>
       </c>
       <c r="R22" t="n">
-        <v>7307333</v>
+        <v>7307280</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2922,7 +2934,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2932,7 +2944,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2963,7 +2975,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135333370</v>
+        <v>135333367</v>
       </c>
       <c r="B23" t="n">
         <v>83222</v>
@@ -2998,13 +3010,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>624014</v>
+        <v>624036</v>
       </c>
       <c r="R23" t="n">
-        <v>7307360</v>
+        <v>7307333</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3033,7 +3045,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3043,7 +3055,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3074,7 +3086,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135333377</v>
+        <v>135333370</v>
       </c>
       <c r="B24" t="n">
         <v>83222</v>
@@ -3109,13 +3121,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>623784</v>
+        <v>624014</v>
       </c>
       <c r="R24" t="n">
-        <v>7307352</v>
+        <v>7307360</v>
       </c>
       <c r="S24" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3144,7 +3156,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3154,7 +3166,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3185,10 +3197,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135331135</v>
+        <v>135333377</v>
       </c>
       <c r="B25" t="n">
-        <v>92167</v>
+        <v>83222</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3196,37 +3208,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1588</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>623561</v>
+        <v>623784</v>
       </c>
       <c r="R25" t="n">
-        <v>7307325</v>
+        <v>7307352</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3255,7 +3267,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3265,7 +3277,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3280,12 +3292,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3296,7 +3308,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135331140</v>
+        <v>135331135</v>
       </c>
       <c r="B26" t="n">
         <v>92167</v>
@@ -3331,13 +3343,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>623575</v>
+        <v>623561</v>
       </c>
       <c r="R26" t="n">
-        <v>7307427</v>
+        <v>7307325</v>
       </c>
       <c r="S26" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3366,7 +3378,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3376,7 +3388,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3407,32 +3419,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135331131</v>
+        <v>135331140</v>
       </c>
       <c r="B27" t="n">
-        <v>96678</v>
+        <v>92167</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2166</v>
+        <v>1588</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skör kvastmossa</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dicranum fragilifolium</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Lindb.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3442,13 +3454,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>623557</v>
+        <v>623575</v>
       </c>
       <c r="R27" t="n">
-        <v>7307301</v>
+        <v>7307427</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3477,7 +3489,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3487,7 +3499,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3518,10 +3530,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135331132</v>
+        <v>135331131</v>
       </c>
       <c r="B28" t="n">
-        <v>97308</v>
+        <v>96678</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3529,21 +3541,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2869</v>
+        <v>2166</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Skör kvastmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Dicranum fragilifolium</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>Lindb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3553,13 +3565,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>623545</v>
+        <v>623557</v>
       </c>
       <c r="R28" t="n">
-        <v>7307305</v>
+        <v>7307301</v>
       </c>
       <c r="S28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3629,32 +3641,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135331123</v>
+        <v>135331132</v>
       </c>
       <c r="B29" t="n">
-        <v>91896</v>
+        <v>97308</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3242</v>
+        <v>2869</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3664,13 +3676,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>623681</v>
+        <v>623545</v>
       </c>
       <c r="R29" t="n">
-        <v>7307293</v>
+        <v>7307305</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3699,7 +3711,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3709,7 +3721,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3740,48 +3752,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135320627</v>
+        <v>135331123</v>
       </c>
       <c r="B30" t="n">
-        <v>91937</v>
+        <v>91896</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>3242</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Grundträsk, Grundträsk, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>623517</v>
+        <v>623681</v>
       </c>
       <c r="R30" t="n">
-        <v>7307459</v>
+        <v>7307293</v>
       </c>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3810,7 +3822,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3820,7 +3832,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3835,19 +3847,23 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
+          <t>Laura Dobrandt</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135332769</v>
+        <v>135320627</v>
       </c>
       <c r="B31" t="n">
         <v>91937</v>
@@ -3878,17 +3894,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Grundträsk, Grundträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>624069</v>
+        <v>623517</v>
       </c>
       <c r="R31" t="n">
-        <v>7307267</v>
+        <v>7307459</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3917,7 +3933,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3927,7 +3943,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3942,64 +3958,60 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135319473</v>
+        <v>135332769</v>
       </c>
       <c r="B32" t="n">
-        <v>79373</v>
+        <v>91937</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Grundträsk, Grundträsk, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>623472</v>
+        <v>624069</v>
       </c>
       <c r="R32" t="n">
-        <v>7307510</v>
+        <v>7307267</v>
       </c>
       <c r="S32" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4028,7 +4040,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4038,7 +4050,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4053,19 +4065,23 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135319562</v>
+        <v>135319473</v>
       </c>
       <c r="B33" t="n">
         <v>79373</v>
@@ -4100,10 +4116,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>623499</v>
+        <v>623472</v>
       </c>
       <c r="R33" t="n">
-        <v>7307488</v>
+        <v>7307510</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4135,7 +4151,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4145,7 +4161,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4172,7 +4188,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135331027</v>
+        <v>135319562</v>
       </c>
       <c r="B34" t="n">
         <v>79373</v>
@@ -4203,17 +4219,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Nära Änganäs, Pi lm</t>
+          <t>Grundträsk, Grundträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>623680</v>
+        <v>623499</v>
       </c>
       <c r="R34" t="n">
-        <v>7307293</v>
+        <v>7307487</v>
       </c>
       <c r="S34" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4240,9 +4256,19 @@
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4257,23 +4283,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135331029</v>
+        <v>135331027</v>
       </c>
       <c r="B35" t="n">
         <v>79373</v>
@@ -4308,13 +4330,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>623660</v>
+        <v>623680</v>
       </c>
       <c r="R35" t="n">
-        <v>7307297</v>
+        <v>7307293</v>
       </c>
       <c r="S35" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4374,7 +4396,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135331670</v>
+        <v>135331029</v>
       </c>
       <c r="B36" t="n">
         <v>79373</v>
@@ -4405,17 +4427,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Nära Änganäs, Pi lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>624012</v>
+        <v>623660</v>
       </c>
       <c r="R36" t="n">
-        <v>7307326</v>
+        <v>7307297</v>
       </c>
       <c r="S36" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4442,19 +4464,9 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>15:47</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>15:47</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4469,12 +4481,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4485,7 +4497,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135333184</v>
+        <v>135331130</v>
       </c>
       <c r="B37" t="n">
         <v>79373</v>
@@ -4514,19 +4526,22 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>623581</v>
+        <v>623561</v>
       </c>
       <c r="R37" t="n">
-        <v>7307301</v>
+        <v>7307299</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4555,7 +4570,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4565,7 +4580,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4574,18 +4589,19 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4596,7 +4612,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135333188</v>
+        <v>135331350</v>
       </c>
       <c r="B38" t="n">
         <v>79373</v>
@@ -4627,17 +4643,17 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>623541</v>
+        <v>623938</v>
       </c>
       <c r="R38" t="n">
-        <v>7307359</v>
+        <v>7307328</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4666,7 +4682,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4676,7 +4692,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4691,12 +4707,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4707,7 +4723,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135333190</v>
+        <v>135331670</v>
       </c>
       <c r="B39" t="n">
         <v>79373</v>
@@ -4738,17 +4754,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>623521</v>
+        <v>624012</v>
       </c>
       <c r="R39" t="n">
-        <v>7307382</v>
+        <v>7307326</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4777,7 +4793,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4787,7 +4803,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4802,12 +4818,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4818,48 +4834,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135320009</v>
+        <v>135333184</v>
       </c>
       <c r="B40" t="n">
-        <v>78776</v>
+        <v>79373</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Grundträsk, Grundträsk, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>623461</v>
+        <v>623581</v>
       </c>
       <c r="R40" t="n">
-        <v>7307589</v>
+        <v>7307301</v>
       </c>
       <c r="S40" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4888,7 +4904,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4898,7 +4914,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4913,57 +4929,61 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135331033</v>
+        <v>135333188</v>
       </c>
       <c r="B41" t="n">
-        <v>78776</v>
+        <v>79373</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Nära Änganäs, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>623649</v>
+        <v>623541</v>
       </c>
       <c r="R41" t="n">
-        <v>7307278</v>
+        <v>7307359</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4993,9 +5013,19 @@
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5010,12 +5040,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5026,45 +5056,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135333364</v>
+        <v>135333190</v>
       </c>
       <c r="B42" t="n">
-        <v>78776</v>
+        <v>79373</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>624037</v>
+        <v>623521</v>
       </c>
       <c r="R42" t="n">
-        <v>7307285</v>
+        <v>7307382</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5096,7 +5126,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5106,7 +5136,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5121,12 +5151,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5137,7 +5167,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135333375</v>
+        <v>135320009</v>
       </c>
       <c r="B43" t="n">
         <v>78776</v>
@@ -5168,17 +5198,17 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Grundträsk, Grundträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>623832</v>
+        <v>623461</v>
       </c>
       <c r="R43" t="n">
-        <v>7307315</v>
+        <v>7307589</v>
       </c>
       <c r="S43" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5207,7 +5237,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5217,7 +5247,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5232,26 +5262,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135332772</v>
+        <v>135331033</v>
       </c>
       <c r="B44" t="n">
-        <v>83358</v>
+        <v>78776</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5259,37 +5285,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Nära Änganäs, Pi lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>624017</v>
+        <v>623649</v>
       </c>
       <c r="R44" t="n">
-        <v>7307324</v>
+        <v>7307278</v>
       </c>
       <c r="S44" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5316,19 +5342,9 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>15:49</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5343,12 +5359,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5359,10 +5375,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135332775</v>
+        <v>135333364</v>
       </c>
       <c r="B45" t="n">
-        <v>83358</v>
+        <v>78776</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5370,21 +5386,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5394,10 +5410,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>623971</v>
+        <v>624037</v>
       </c>
       <c r="R45" t="n">
-        <v>7307331</v>
+        <v>7307285</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5429,7 +5445,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5439,7 +5455,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5454,12 +5470,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5470,10 +5486,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135333183</v>
+        <v>135333375</v>
       </c>
       <c r="B46" t="n">
-        <v>83358</v>
+        <v>78776</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5481,37 +5497,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>623578</v>
+        <v>623832</v>
       </c>
       <c r="R46" t="n">
-        <v>7307305</v>
+        <v>7307315</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5540,7 +5556,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5550,7 +5566,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5565,12 +5581,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5581,10 +5597,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135319971</v>
+        <v>135358216</v>
       </c>
       <c r="B47" t="n">
-        <v>79992</v>
+        <v>78776</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5592,37 +5608,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Grundträsk, Grundträsk, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>623461</v>
+        <v>624015</v>
       </c>
       <c r="R47" t="n">
-        <v>7307589</v>
+        <v>7307320</v>
       </c>
       <c r="S47" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5651,7 +5667,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5661,7 +5677,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5676,22 +5692,26 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
+          <t>Maja Rancic</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135331035</v>
+        <v>135332772</v>
       </c>
       <c r="B48" t="n">
-        <v>79992</v>
+        <v>83358</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5699,37 +5719,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Nära Änganäs, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>623629</v>
+        <v>624017</v>
       </c>
       <c r="R48" t="n">
-        <v>7307251</v>
+        <v>7307324</v>
       </c>
       <c r="S48" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5756,9 +5776,19 @@
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5773,12 +5803,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5789,10 +5819,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135332771</v>
+        <v>135332775</v>
       </c>
       <c r="B49" t="n">
-        <v>79992</v>
+        <v>83358</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5800,21 +5830,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5824,13 +5854,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>624036</v>
+        <v>623971</v>
       </c>
       <c r="R49" t="n">
-        <v>7307307</v>
+        <v>7307331</v>
       </c>
       <c r="S49" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5859,7 +5889,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5869,7 +5899,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5900,10 +5930,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135332776</v>
+        <v>135333183</v>
       </c>
       <c r="B50" t="n">
-        <v>79992</v>
+        <v>83358</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5911,37 +5941,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>623926</v>
+        <v>623578</v>
       </c>
       <c r="R50" t="n">
-        <v>7307301</v>
+        <v>7307305</v>
       </c>
       <c r="S50" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5970,7 +6000,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5980,7 +6010,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5995,12 +6025,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -6011,7 +6041,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135333181</v>
+        <v>135319971</v>
       </c>
       <c r="B51" t="n">
         <v>79992</v>
@@ -6042,17 +6072,17 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
+          <t>Grundträsk, Grundträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>623638</v>
+        <v>623461</v>
       </c>
       <c r="R51" t="n">
-        <v>7307259</v>
+        <v>7307589</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6081,7 +6111,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6091,7 +6121,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6106,23 +6136,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135333185</v>
+        <v>135331035</v>
       </c>
       <c r="B52" t="n">
         <v>79992</v>
@@ -6153,17 +6179,17 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
+          <t>Nära Änganäs, Pi lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>623521</v>
+        <v>623629</v>
       </c>
       <c r="R52" t="n">
-        <v>7307328</v>
+        <v>7307251</v>
       </c>
       <c r="S52" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6190,19 +6216,9 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>15:07</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>15:07</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6217,12 +6233,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6233,48 +6249,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135333191</v>
+        <v>135332771</v>
       </c>
       <c r="B53" t="n">
-        <v>80500</v>
+        <v>79992</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>623500</v>
+        <v>624036</v>
       </c>
       <c r="R53" t="n">
-        <v>7307377</v>
+        <v>7307307</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6303,7 +6319,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6313,7 +6329,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6328,12 +6344,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6344,32 +6360,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135333371</v>
+        <v>135332776</v>
       </c>
       <c r="B54" t="n">
-        <v>57972</v>
+        <v>79992</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6379,13 +6395,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>624014</v>
+        <v>623926</v>
       </c>
       <c r="R54" t="n">
-        <v>7307360</v>
+        <v>7307301</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6414,7 +6430,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6424,7 +6440,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6439,12 +6455,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6455,48 +6471,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135333374</v>
+        <v>135333181</v>
       </c>
       <c r="B55" t="n">
-        <v>57972</v>
+        <v>79992</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>623919</v>
+        <v>623638</v>
       </c>
       <c r="R55" t="n">
-        <v>7307361</v>
+        <v>7307259</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6525,7 +6541,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6535,12 +6551,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Hack</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6555,12 +6566,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6571,10 +6582,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135318090</v>
+        <v>135333185</v>
       </c>
       <c r="B56" t="n">
-        <v>57975</v>
+        <v>79992</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6582,37 +6593,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Grundträsk, Grundträsk, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>623800</v>
+        <v>623521</v>
       </c>
       <c r="R56" t="n">
-        <v>7307412</v>
+        <v>7307328</v>
       </c>
       <c r="S56" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6641,7 +6652,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6651,7 +6662,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6666,60 +6677,64 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135319479</v>
+        <v>135333191</v>
       </c>
       <c r="B57" t="n">
-        <v>57975</v>
+        <v>80500</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Grundträsk, Grundträsk, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>623472</v>
+        <v>623500</v>
       </c>
       <c r="R57" t="n">
-        <v>7307510</v>
+        <v>7307377</v>
       </c>
       <c r="S57" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6748,7 +6763,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6758,12 +6773,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:05</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Spår</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6778,39 +6788,43 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135319812</v>
+        <v>135333371</v>
       </c>
       <c r="B58" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6821,17 +6835,17 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Grundträsk, Grundträsk, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>623492</v>
+        <v>624014</v>
       </c>
       <c r="R58" t="n">
-        <v>7307534</v>
+        <v>7307360</v>
       </c>
       <c r="S58" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6860,7 +6874,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6870,12 +6884,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Spår</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6890,39 +6899,43 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135320195</v>
+        <v>135333374</v>
       </c>
       <c r="B59" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6933,17 +6946,17 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Grundträsk, Grundträsk, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>623500</v>
+        <v>623919</v>
       </c>
       <c r="R59" t="n">
-        <v>7307689</v>
+        <v>7307361</v>
       </c>
       <c r="S59" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6972,7 +6985,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6982,12 +6995,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Spår</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7002,19 +7015,23 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr"/>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135320511</v>
+        <v>135318090</v>
       </c>
       <c r="B60" t="n">
         <v>57975</v>
@@ -7049,10 +7066,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>623489</v>
+        <v>623800</v>
       </c>
       <c r="R60" t="n">
-        <v>7307496</v>
+        <v>7307412</v>
       </c>
       <c r="S60" t="n">
         <v>1</v>
@@ -7084,7 +7101,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7094,12 +7111,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:58</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Gamla spår</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7126,7 +7138,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135331038</v>
+        <v>135319479</v>
       </c>
       <c r="B61" t="n">
         <v>57975</v>
@@ -7157,17 +7169,17 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Nära Änganäs, Pi lm</t>
+          <t>Grundträsk, Grundträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>623589</v>
+        <v>623472</v>
       </c>
       <c r="R61" t="n">
-        <v>7307264</v>
+        <v>7307510</v>
       </c>
       <c r="S61" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7194,14 +7206,24 @@
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Spår</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7216,23 +7238,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135332777</v>
+        <v>135319812</v>
       </c>
       <c r="B62" t="n">
         <v>57975</v>
@@ -7261,24 +7279,19 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Grundträsk, Grundträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>623904</v>
+        <v>623492</v>
       </c>
       <c r="R62" t="n">
-        <v>7307334</v>
+        <v>7307534</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7307,7 +7320,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7317,7 +7330,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Spår</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7332,23 +7350,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135332781</v>
+        <v>135320195</v>
       </c>
       <c r="B63" t="n">
         <v>57975</v>
@@ -7377,24 +7391,19 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Grundträsk, Grundträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>623790</v>
+        <v>623500</v>
       </c>
       <c r="R63" t="n">
-        <v>7307346</v>
+        <v>7307689</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7423,7 +7432,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7433,7 +7442,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Spår</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7448,23 +7462,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135332783</v>
+        <v>135320511</v>
       </c>
       <c r="B64" t="n">
         <v>57975</v>
@@ -7495,17 +7505,17 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Grundträsk, Grundträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>623971</v>
+        <v>623489</v>
       </c>
       <c r="R64" t="n">
-        <v>7307384</v>
+        <v>7307496</v>
       </c>
       <c r="S64" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7534,7 +7544,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7544,19 +7554,19 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>skalade undertryckta granar, flera stycken</t>
+          <t>Gamla spår</t>
         </is>
       </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG64" t="b">
         <v>0</v>
@@ -7564,23 +7574,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135332786</v>
+        <v>135331038</v>
       </c>
       <c r="B65" t="n">
         <v>57975</v>
@@ -7609,24 +7615,19 @@
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Nära Änganäs, Pi lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>624077</v>
+        <v>623589</v>
       </c>
       <c r="R65" t="n">
-        <v>7307313</v>
+        <v>7307264</v>
       </c>
       <c r="S65" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7653,19 +7654,14 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>16:48</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>16:48</t>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7680,12 +7676,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7696,7 +7692,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135333182</v>
+        <v>135332777</v>
       </c>
       <c r="B66" t="n">
         <v>57975</v>
@@ -7725,16 +7721,21 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>623602</v>
+        <v>623904</v>
       </c>
       <c r="R66" t="n">
-        <v>7307284</v>
+        <v>7307334</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7766,7 +7767,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7776,12 +7777,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:36</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7796,12 +7792,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7812,45 +7808,50 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135331121</v>
+        <v>135332781</v>
       </c>
       <c r="B67" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>623943</v>
+        <v>623790</v>
       </c>
       <c r="R67" t="n">
-        <v>7307296</v>
+        <v>7307346</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7882,7 +7883,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7892,7 +7893,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7907,12 +7908,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7923,48 +7924,48 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135331122</v>
+        <v>135332783</v>
       </c>
       <c r="B68" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>623926</v>
+        <v>623971</v>
       </c>
       <c r="R68" t="n">
-        <v>7307337</v>
+        <v>7307384</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7993,7 +7994,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8003,19 +8004,19 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Tjäderbo? eller uppehallsplats?</t>
+          <t>skalade undertryckta granar, flera stycken</t>
         </is>
       </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG68" t="b">
         <v>0</v>
@@ -8023,12 +8024,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -8039,48 +8040,53 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135331032</v>
+        <v>135332786</v>
       </c>
       <c r="B69" t="n">
-        <v>5181</v>
+        <v>57975</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Nära Änganäs, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>623649</v>
+        <v>624077</v>
       </c>
       <c r="R69" t="n">
-        <v>7307278</v>
+        <v>7307313</v>
       </c>
       <c r="S69" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8107,14 +8113,19 @@
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Gnag</t>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8129,12 +8140,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -8145,45 +8156,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135333376</v>
+        <v>135333182</v>
       </c>
       <c r="B70" t="n">
-        <v>5181</v>
+        <v>57975</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>623799</v>
+        <v>623602</v>
       </c>
       <c r="R70" t="n">
-        <v>7307327</v>
+        <v>7307284</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8215,7 +8226,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8225,12 +8236,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Gnag</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8245,12 +8256,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -8261,10 +8272,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135332770</v>
+        <v>135337852</v>
       </c>
       <c r="B71" t="n">
-        <v>58136</v>
+        <v>57975</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8272,37 +8283,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>624031</v>
+        <v>623747</v>
       </c>
       <c r="R71" t="n">
-        <v>7307306</v>
+        <v>7307427</v>
       </c>
       <c r="S71" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8331,7 +8342,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8341,7 +8352,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8356,12 +8372,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -8372,10 +8388,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135333365</v>
+        <v>135337854</v>
       </c>
       <c r="B72" t="n">
-        <v>58136</v>
+        <v>57975</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8383,37 +8399,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>624039</v>
+        <v>623570</v>
       </c>
       <c r="R72" t="n">
-        <v>7307316</v>
+        <v>7307448</v>
       </c>
       <c r="S72" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8442,7 +8458,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8452,7 +8468,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Spår</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8467,12 +8488,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8483,10 +8504,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135333378</v>
+        <v>135337855</v>
       </c>
       <c r="B73" t="n">
-        <v>58136</v>
+        <v>57975</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8494,37 +8515,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>624079</v>
+        <v>623573</v>
       </c>
       <c r="R73" t="n">
-        <v>7307360</v>
+        <v>7307467</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8553,7 +8574,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8563,12 +8584,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Familjegrupp, minst 5 st</t>
+          <t>Spår</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8583,12 +8604,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8599,27 +8620,27 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135331030</v>
+        <v>135337857</v>
       </c>
       <c r="B74" t="n">
-        <v>5201</v>
+        <v>57975</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>105930</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -8628,19 +8649,23 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Nära Änganäs, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>623665</v>
+        <v>623573</v>
       </c>
       <c r="R74" t="n">
-        <v>7307294</v>
+        <v>7307487</v>
       </c>
       <c r="S74" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8667,14 +8692,24 @@
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Gnag</t>
+          <t>Spår på två träd</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8689,12 +8724,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8705,10 +8740,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135333372</v>
+        <v>135331121</v>
       </c>
       <c r="B75" t="n">
-        <v>99099</v>
+        <v>57162</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8716,34 +8751,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220093</v>
+        <v>100138</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>624008</v>
+        <v>623943</v>
       </c>
       <c r="R75" t="n">
-        <v>7307352</v>
+        <v>7307296</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8775,7 +8810,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8785,12 +8820,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Kolla</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8805,12 +8835,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8821,10 +8851,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135319835</v>
+        <v>135331122</v>
       </c>
       <c r="B76" t="n">
-        <v>98060</v>
+        <v>57162</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8832,37 +8862,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Grundträsk, Grundträsk, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>623492</v>
+        <v>623926</v>
       </c>
       <c r="R76" t="n">
-        <v>7307534</v>
+        <v>7307337</v>
       </c>
       <c r="S76" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8891,7 +8921,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8901,7 +8931,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Tjäderbo? eller uppehallsplats?</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8916,22 +8951,26 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr"/>
+          <t>Laura Dobrandt</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135331671</v>
+        <v>135331032</v>
       </c>
       <c r="B77" t="n">
-        <v>98060</v>
+        <v>5181</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8939,37 +8978,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Nära Änganäs, Pi lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>623997</v>
+        <v>623649</v>
       </c>
       <c r="R77" t="n">
-        <v>7307348</v>
+        <v>7307278</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8996,19 +9035,14 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>15:57</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>15:57</t>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Gnag</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9023,12 +9057,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -9039,10 +9073,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135331145</v>
+        <v>135333376</v>
       </c>
       <c r="B78" t="n">
-        <v>99217</v>
+        <v>5181</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9050,37 +9084,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221952</v>
+        <v>100526</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>623644</v>
+        <v>623799</v>
       </c>
       <c r="R78" t="n">
-        <v>7307354</v>
+        <v>7307327</v>
       </c>
       <c r="S78" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9109,7 +9143,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9119,7 +9153,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Gnag</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9134,12 +9173,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -9150,48 +9189,48 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>135331672</v>
+        <v>135332770</v>
       </c>
       <c r="B79" t="n">
-        <v>99217</v>
+        <v>58136</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>624001</v>
+        <v>624031</v>
       </c>
       <c r="R79" t="n">
-        <v>7307352</v>
+        <v>7307306</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9220,7 +9259,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9230,7 +9269,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9245,12 +9284,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -9261,48 +9300,48 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>135331673</v>
+        <v>135333365</v>
       </c>
       <c r="B80" t="n">
-        <v>99217</v>
+        <v>58136</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>623969</v>
+        <v>624039</v>
       </c>
       <c r="R80" t="n">
-        <v>7307338</v>
+        <v>7307316</v>
       </c>
       <c r="S80" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9331,7 +9370,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9341,7 +9380,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9356,12 +9395,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -9372,48 +9411,48 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>135331674</v>
+        <v>135333378</v>
       </c>
       <c r="B81" t="n">
-        <v>99217</v>
+        <v>58136</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>623948</v>
+        <v>624079</v>
       </c>
       <c r="R81" t="n">
-        <v>7307327</v>
+        <v>7307360</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9442,7 +9481,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9452,7 +9491,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Familjegrupp, minst 5 st</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9467,12 +9511,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -9483,32 +9527,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>135331039</v>
+        <v>135331030</v>
       </c>
       <c r="B82" t="n">
-        <v>79963</v>
+        <v>5201</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229821</v>
+        <v>105930</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9518,13 +9562,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>623714</v>
+        <v>623665</v>
       </c>
       <c r="R82" t="n">
-        <v>7307148</v>
+        <v>7307294</v>
       </c>
       <c r="S82" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9554,6 +9598,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Gnag</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9584,45 +9633,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>135331124</v>
+        <v>135333372</v>
       </c>
       <c r="B83" t="n">
-        <v>79963</v>
+        <v>99099</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>229821</v>
+        <v>220093</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>623675</v>
+        <v>624008</v>
       </c>
       <c r="R83" t="n">
-        <v>7307271</v>
+        <v>7307352</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9654,7 +9703,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9664,7 +9713,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Kolla</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9679,12 +9733,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9695,48 +9749,48 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>135331125</v>
+        <v>135337862</v>
       </c>
       <c r="B84" t="n">
-        <v>79963</v>
+        <v>106309</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>229821</v>
+        <v>221725</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>623635</v>
+        <v>623573</v>
       </c>
       <c r="R84" t="n">
-        <v>7307226</v>
+        <v>7307459</v>
       </c>
       <c r="S84" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9760,27 +9814,22 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Stubbe med yxhugg ser bild</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9795,12 +9844,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9811,48 +9860,48 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>135331126</v>
+        <v>135319835</v>
       </c>
       <c r="B85" t="n">
-        <v>79963</v>
+        <v>98060</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>229821</v>
+        <v>221945</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Grundträsk, Grundträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>623584</v>
+        <v>623492</v>
       </c>
       <c r="R85" t="n">
-        <v>7307249</v>
+        <v>7307534</v>
       </c>
       <c r="S85" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9881,7 +9930,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9891,7 +9940,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9906,64 +9955,60 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
-        </is>
-      </c>
-      <c r="AY85" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>135331128</v>
+        <v>135331671</v>
       </c>
       <c r="B86" t="n">
-        <v>79963</v>
+        <v>98060</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>229821</v>
+        <v>221945</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>623566</v>
+        <v>623997</v>
       </c>
       <c r="R86" t="n">
-        <v>7307255</v>
+        <v>7307348</v>
       </c>
       <c r="S86" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9992,7 +10037,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10002,7 +10047,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10017,12 +10062,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -10033,48 +10078,48 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>135333186</v>
+        <v>135331145</v>
       </c>
       <c r="B87" t="n">
-        <v>79963</v>
+        <v>99217</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229821</v>
+        <v>221952</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>623526</v>
+        <v>623644</v>
       </c>
       <c r="R87" t="n">
-        <v>7307330</v>
+        <v>7307354</v>
       </c>
       <c r="S87" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10103,7 +10148,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10113,7 +10158,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10128,12 +10173,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -10144,45 +10189,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>135331119</v>
+        <v>135331672</v>
       </c>
       <c r="B88" t="n">
-        <v>79396</v>
+        <v>99217</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>260591</v>
+        <v>221952</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>624074</v>
+        <v>624001</v>
       </c>
       <c r="R88" t="n">
-        <v>7307283</v>
+        <v>7307352</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10214,7 +10259,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10224,7 +10269,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10233,19 +10278,18 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -10256,32 +10300,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>135331669</v>
+        <v>135331673</v>
       </c>
       <c r="B89" t="n">
-        <v>79396</v>
+        <v>99217</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>260591</v>
+        <v>221952</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10291,13 +10335,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>624037</v>
+        <v>623969</v>
       </c>
       <c r="R89" t="n">
-        <v>7307291</v>
+        <v>7307338</v>
       </c>
       <c r="S89" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10326,7 +10370,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10336,7 +10380,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10367,45 +10411,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>135332778</v>
+        <v>135331674</v>
       </c>
       <c r="B90" t="n">
-        <v>79396</v>
+        <v>99217</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>260591</v>
+        <v>221952</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>623849</v>
+        <v>623948</v>
       </c>
       <c r="R90" t="n">
-        <v>7307318</v>
+        <v>7307327</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10437,7 +10481,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10447,7 +10491,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10462,12 +10506,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -10478,10 +10522,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>135333180</v>
+        <v>135331039</v>
       </c>
       <c r="B91" t="n">
-        <v>79396</v>
+        <v>79963</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10489,37 +10533,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>260591</v>
+        <v>229821</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
+          <t>Nära Änganäs, Pi lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>623673</v>
+        <v>623714</v>
       </c>
       <c r="R91" t="n">
-        <v>7307275</v>
+        <v>7307148</v>
       </c>
       <c r="S91" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10546,19 +10590,9 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>14:29</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10573,12 +10607,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10589,10 +10623,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>135333382</v>
+        <v>135331124</v>
       </c>
       <c r="B92" t="n">
-        <v>79396</v>
+        <v>79963</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10600,37 +10634,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>260591</v>
+        <v>229821</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>624084</v>
+        <v>623675</v>
       </c>
       <c r="R92" t="n">
-        <v>7307323</v>
+        <v>7307271</v>
       </c>
       <c r="S92" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10659,7 +10693,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10669,7 +10703,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10684,15 +10718,1020 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
+          <t>Laura Dobrandt</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Laura Dobrandt</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>135331125</v>
+      </c>
+      <c r="B93" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>623635</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7307226</v>
+      </c>
+      <c r="S93" t="n">
+        <v>9</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Stubbe med yxhugg ser bild</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Laura Dobrandt</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Laura Dobrandt</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>135331126</v>
+      </c>
+      <c r="B94" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>623584</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7307249</v>
+      </c>
+      <c r="S94" t="n">
+        <v>12</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Laura Dobrandt</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Laura Dobrandt</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>135331128</v>
+      </c>
+      <c r="B95" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>623566</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7307255</v>
+      </c>
+      <c r="S95" t="n">
+        <v>6</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Laura Dobrandt</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Laura Dobrandt</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>135333186</v>
+      </c>
+      <c r="B96" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>623526</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7307330</v>
+      </c>
+      <c r="S96" t="n">
+        <v>6</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>135331119</v>
+      </c>
+      <c r="B97" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>624074</v>
+      </c>
+      <c r="R97" t="n">
+        <v>7307283</v>
+      </c>
+      <c r="S97" t="n">
+        <v>5</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Laura Dobrandt</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Laura Dobrandt</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>135331669</v>
+      </c>
+      <c r="B98" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Tsågávvrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>624037</v>
+      </c>
+      <c r="R98" t="n">
+        <v>7307291</v>
+      </c>
+      <c r="S98" t="n">
+        <v>6</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>135332778</v>
+      </c>
+      <c r="B99" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Tsågávvrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>623849</v>
+      </c>
+      <c r="R99" t="n">
+        <v>7307318</v>
+      </c>
+      <c r="S99" t="n">
+        <v>5</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>135333180</v>
+      </c>
+      <c r="B100" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>623673</v>
+      </c>
+      <c r="R100" t="n">
+        <v>7307275</v>
+      </c>
+      <c r="S100" t="n">
+        <v>7</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>135333382</v>
+      </c>
+      <c r="B101" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Tsågávvrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>624084</v>
+      </c>
+      <c r="R101" t="n">
+        <v>7307323</v>
+      </c>
+      <c r="S101" t="n">
+        <v>6</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
           <t>Linda Nordström</t>
         </is>
       </c>
-      <c r="AX92" t="inlineStr">
+      <c r="AX101" t="inlineStr">
         <is>
           <t>Linda Nordström</t>
         </is>
       </c>
-      <c r="AY92" t="inlineStr">
+      <c r="AY101" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>

--- a/artfynd/A 64809-2023 artfynd.xlsx
+++ b/artfynd/A 64809-2023 artfynd.xlsx
@@ -4226,7 +4226,7 @@
         <v>623499</v>
       </c>
       <c r="R34" t="n">
-        <v>7307487</v>
+        <v>7307488</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>

--- a/artfynd/A 64809-2023 artfynd.xlsx
+++ b/artfynd/A 64809-2023 artfynd.xlsx
@@ -4226,7 +4226,7 @@
         <v>623499</v>
       </c>
       <c r="R34" t="n">
-        <v>7307488</v>
+        <v>7307487</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>

--- a/artfynd/A 64809-2023 artfynd.xlsx
+++ b/artfynd/A 64809-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY101"/>
+  <dimension ref="A1:AZ101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331137</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331143</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,6 +1016,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331036</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332782</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1224,6 +1249,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331144</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1335,6 +1365,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331133</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1446,6 +1481,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331136</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1557,6 +1597,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333192</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1668,6 +1713,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333369</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1779,6 +1829,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333193</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1890,6 +1945,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333379</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2007,6 +2067,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135337856</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2108,6 +2173,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331034</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2209,6 +2279,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331031</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2320,6 +2395,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333195</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2437,6 +2517,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135337861</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2538,6 +2623,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331028</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2639,6 +2729,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331037</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2750,6 +2845,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331141</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2861,6 +2961,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332774</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2972,6 +3077,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333363</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3083,6 +3193,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333367</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3194,6 +3309,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333370</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3305,6 +3425,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333377</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3416,6 +3541,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331135</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3527,6 +3657,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331140</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3638,6 +3773,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331131</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3749,6 +3889,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331132</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3860,6 +4005,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331123</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3967,6 +4117,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135320627</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4078,6 +4233,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332769</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4185,6 +4345,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135319473</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4226,7 +4391,7 @@
         <v>623499</v>
       </c>
       <c r="R34" t="n">
-        <v>7307488</v>
+        <v>7307487</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4292,6 +4457,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135319562</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4393,6 +4563,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331027</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4492,6 +4667,11 @@
       <c r="AY36" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331029</t>
         </is>
       </c>
     </row>
@@ -4609,6 +4789,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331130</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4720,6 +4905,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331350</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4831,6 +5021,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331670</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4942,6 +5137,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333184</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5053,6 +5253,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333188</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5164,6 +5369,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333190</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5271,6 +5481,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135320009</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5372,6 +5587,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331033</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5483,6 +5703,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333364</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5594,6 +5819,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333375</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5705,6 +5935,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358216</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5816,6 +6051,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332772</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5927,6 +6167,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332775</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6038,6 +6283,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333183</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6145,6 +6395,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135319971</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6246,6 +6501,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331035</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6357,6 +6617,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332771</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6468,6 +6733,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332776</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6579,6 +6849,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333181</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6690,6 +6965,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333185</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6801,6 +7081,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333191</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6912,6 +7197,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333371</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7028,6 +7318,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333374</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7135,6 +7430,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135318090</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7247,6 +7547,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135319479</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7359,6 +7664,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135319812</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7471,6 +7781,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135320195</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7583,6 +7898,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135320511</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7689,6 +8009,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331038</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7805,6 +8130,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332777</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7921,6 +8251,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332781</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8037,6 +8372,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332783</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8153,6 +8493,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332786</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8269,6 +8614,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333182</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8385,6 +8735,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135337852</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8501,6 +8856,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135337854</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8615,6 +8975,11 @@
       <c r="AY73" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135337855</t>
         </is>
       </c>
     </row>
@@ -8737,6 +9102,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135337857</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8848,6 +9218,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331121</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8964,6 +9339,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331122</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9070,6 +9450,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331032</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9186,6 +9571,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333376</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9297,6 +9687,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332770</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9408,6 +9803,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333365</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9524,6 +9924,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333378</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9630,6 +10035,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331030</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9746,6 +10156,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333372</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9857,6 +10272,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135337862</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9964,6 +10384,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135319835</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10075,6 +10500,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331671</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10186,6 +10616,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331145</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10297,6 +10732,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331672</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10408,6 +10848,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331673</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10519,6 +10964,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331674</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10620,6 +11070,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331039</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10731,6 +11186,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331124</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10847,6 +11307,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331125</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10958,6 +11423,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331126</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11069,6 +11539,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331128</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11180,6 +11655,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333186</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11292,6 +11772,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331119</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11403,6 +11888,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331669</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11514,6 +12004,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332778</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11625,6 +12120,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333180</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11736,8 +12236,115 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333382</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 64809-2023 artfynd.xlsx
+++ b/artfynd/A 64809-2023 artfynd.xlsx
@@ -4391,7 +4391,7 @@
         <v>623499</v>
       </c>
       <c r="R34" t="n">
-        <v>7307487</v>
+        <v>7307488</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>

--- a/artfynd/A 64809-2023 artfynd.xlsx
+++ b/artfynd/A 64809-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135331137</v>
       </c>
       <c r="B2" t="n">
-        <v>83343</v>
+        <v>83383</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>135331143</v>
       </c>
       <c r="B3" t="n">
-        <v>83350</v>
+        <v>83390</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>135331036</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>135332782</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>135331144</v>
       </c>
       <c r="B6" t="n">
-        <v>83349</v>
+        <v>83389</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>135331133</v>
       </c>
       <c r="B7" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>135331136</v>
       </c>
       <c r="B8" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>135333192</v>
       </c>
       <c r="B9" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>135333369</v>
       </c>
       <c r="B10" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>135333193</v>
       </c>
       <c r="B11" t="n">
-        <v>92795</v>
+        <v>92837</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>135333379</v>
       </c>
       <c r="B12" t="n">
-        <v>92795</v>
+        <v>92837</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>135337856</v>
       </c>
       <c r="B13" t="n">
-        <v>92795</v>
+        <v>92837</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>135331034</v>
       </c>
       <c r="B14" t="n">
-        <v>81355</v>
+        <v>81393</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>135331031</v>
       </c>
       <c r="B15" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>135333195</v>
       </c>
       <c r="B16" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>135337861</v>
       </c>
       <c r="B17" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>135331028</v>
       </c>
       <c r="B18" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>135331037</v>
       </c>
       <c r="B19" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>135331141</v>
       </c>
       <c r="B20" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>135332774</v>
       </c>
       <c r="B21" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>135333363</v>
       </c>
       <c r="B22" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>135333367</v>
       </c>
       <c r="B23" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>135333370</v>
       </c>
       <c r="B24" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>135333377</v>
       </c>
       <c r="B25" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>135331135</v>
       </c>
       <c r="B26" t="n">
-        <v>92167</v>
+        <v>92209</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>135331140</v>
       </c>
       <c r="B27" t="n">
-        <v>92167</v>
+        <v>92209</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>135331131</v>
       </c>
       <c r="B28" t="n">
-        <v>96678</v>
+        <v>96722</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>135331132</v>
       </c>
       <c r="B29" t="n">
-        <v>97308</v>
+        <v>97352</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         <v>135331123</v>
       </c>
       <c r="B30" t="n">
-        <v>91896</v>
+        <v>91938</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
         <v>135320627</v>
       </c>
       <c r="B31" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>135332769</v>
       </c>
       <c r="B32" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>135319473</v>
       </c>
       <c r="B33" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
         <v>135319562</v>
       </c>
       <c r="B34" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>135331027</v>
       </c>
       <c r="B35" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>135331029</v>
       </c>
       <c r="B36" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>135331130</v>
       </c>
       <c r="B37" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>135331350</v>
       </c>
       <c r="B38" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>135331670</v>
       </c>
       <c r="B39" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         <v>135333184</v>
       </c>
       <c r="B40" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
         <v>135333188</v>
       </c>
       <c r="B41" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>135333190</v>
       </c>
       <c r="B42" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         <v>135320009</v>
       </c>
       <c r="B43" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         <v>135331033</v>
       </c>
       <c r="B44" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>135333364</v>
       </c>
       <c r="B45" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         <v>135333375</v>
       </c>
       <c r="B46" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>135358216</v>
       </c>
       <c r="B47" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         <v>135332772</v>
       </c>
       <c r="B48" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
         <v>135332775</v>
       </c>
       <c r="B49" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6178,7 +6178,7 @@
         <v>135333183</v>
       </c>
       <c r="B50" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         <v>135319971</v>
       </c>
       <c r="B51" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>135331035</v>
       </c>
       <c r="B52" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>135332771</v>
       </c>
       <c r="B53" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6628,7 +6628,7 @@
         <v>135332776</v>
       </c>
       <c r="B54" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>135333181</v>
       </c>
       <c r="B55" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6860,7 +6860,7 @@
         <v>135333185</v>
       </c>
       <c r="B56" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         <v>135333191</v>
       </c>
       <c r="B57" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>135333371</v>
       </c>
       <c r="B58" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
         <v>135333374</v>
       </c>
       <c r="B59" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7329,7 +7329,7 @@
         <v>135318090</v>
       </c>
       <c r="B60" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>135319479</v>
       </c>
       <c r="B61" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>135319812</v>
       </c>
       <c r="B62" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
         <v>135320195</v>
       </c>
       <c r="B63" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>135320511</v>
       </c>
       <c r="B64" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7909,7 +7909,7 @@
         <v>135331038</v>
       </c>
       <c r="B65" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8020,7 +8020,7 @@
         <v>135332777</v>
       </c>
       <c r="B66" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         <v>135332781</v>
       </c>
       <c r="B67" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         <v>135332783</v>
       </c>
       <c r="B68" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>135332786</v>
       </c>
       <c r="B69" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
         <v>135333182</v>
       </c>
       <c r="B70" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>135337852</v>
       </c>
       <c r="B71" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8746,7 +8746,7 @@
         <v>135337854</v>
       </c>
       <c r="B72" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>135337855</v>
       </c>
       <c r="B73" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>135337857</v>
       </c>
       <c r="B74" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9113,7 +9113,7 @@
         <v>135331121</v>
       </c>
       <c r="B75" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9229,7 +9229,7 @@
         <v>135331122</v>
       </c>
       <c r="B76" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>135332770</v>
       </c>
       <c r="B79" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9698,7 +9698,7 @@
         <v>135333365</v>
       </c>
       <c r="B80" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
         <v>135333378</v>
       </c>
       <c r="B81" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10046,7 +10046,7 @@
         <v>135333372</v>
       </c>
       <c r="B83" t="n">
-        <v>99099</v>
+        <v>99146</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10167,7 +10167,7 @@
         <v>135337862</v>
       </c>
       <c r="B84" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10283,7 +10283,7 @@
         <v>135319835</v>
       </c>
       <c r="B85" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10395,7 +10395,7 @@
         <v>135331671</v>
       </c>
       <c r="B86" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
         <v>135331145</v>
       </c>
       <c r="B87" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>135331672</v>
       </c>
       <c r="B88" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10743,7 +10743,7 @@
         <v>135331673</v>
       </c>
       <c r="B89" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>135331674</v>
       </c>
       <c r="B90" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10975,7 +10975,7 @@
         <v>135331039</v>
       </c>
       <c r="B91" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11081,7 +11081,7 @@
         <v>135331124</v>
       </c>
       <c r="B92" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11197,7 +11197,7 @@
         <v>135331125</v>
       </c>
       <c r="B93" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11318,7 +11318,7 @@
         <v>135331126</v>
       </c>
       <c r="B94" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11434,7 +11434,7 @@
         <v>135331128</v>
       </c>
       <c r="B95" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11550,7 +11550,7 @@
         <v>135333186</v>
       </c>
       <c r="B96" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11666,7 +11666,7 @@
         <v>135331119</v>
       </c>
       <c r="B97" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>135331669</v>
       </c>
       <c r="B98" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11899,7 +11899,7 @@
         <v>135332778</v>
       </c>
       <c r="B99" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12015,7 +12015,7 @@
         <v>135333180</v>
       </c>
       <c r="B100" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12131,7 +12131,7 @@
         <v>135333382</v>
       </c>
       <c r="B101" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 64809-2023 artfynd.xlsx
+++ b/artfynd/A 64809-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135331137</v>
       </c>
       <c r="B2" t="n">
-        <v>83383</v>
+        <v>83410</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>135331143</v>
       </c>
       <c r="B3" t="n">
-        <v>83390</v>
+        <v>83417</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>135331036</v>
       </c>
       <c r="B4" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>135332782</v>
       </c>
       <c r="B5" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>135331144</v>
       </c>
       <c r="B6" t="n">
-        <v>83389</v>
+        <v>83416</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>135331133</v>
       </c>
       <c r="B7" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>135331136</v>
       </c>
       <c r="B8" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>135333192</v>
       </c>
       <c r="B9" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>135333369</v>
       </c>
       <c r="B10" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>135333193</v>
       </c>
       <c r="B11" t="n">
-        <v>92837</v>
+        <v>92864</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>135333379</v>
       </c>
       <c r="B12" t="n">
-        <v>92837</v>
+        <v>92864</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>135337856</v>
       </c>
       <c r="B13" t="n">
-        <v>92837</v>
+        <v>92864</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>135331034</v>
       </c>
       <c r="B14" t="n">
-        <v>81393</v>
+        <v>81420</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>135331031</v>
       </c>
       <c r="B15" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>135333195</v>
       </c>
       <c r="B16" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>135337861</v>
       </c>
       <c r="B17" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>135331028</v>
       </c>
       <c r="B18" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>135331037</v>
       </c>
       <c r="B19" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>135331141</v>
       </c>
       <c r="B20" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>135332774</v>
       </c>
       <c r="B21" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>135333363</v>
       </c>
       <c r="B22" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>135333367</v>
       </c>
       <c r="B23" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>135333370</v>
       </c>
       <c r="B24" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>135333377</v>
       </c>
       <c r="B25" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>135331135</v>
       </c>
       <c r="B26" t="n">
-        <v>92209</v>
+        <v>92236</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>135331140</v>
       </c>
       <c r="B27" t="n">
-        <v>92209</v>
+        <v>92236</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>135331131</v>
       </c>
       <c r="B28" t="n">
-        <v>96722</v>
+        <v>96749</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>135331132</v>
       </c>
       <c r="B29" t="n">
-        <v>97352</v>
+        <v>97379</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         <v>135331123</v>
       </c>
       <c r="B30" t="n">
-        <v>91938</v>
+        <v>91965</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
         <v>135320627</v>
       </c>
       <c r="B31" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>135332769</v>
       </c>
       <c r="B32" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>135319473</v>
       </c>
       <c r="B33" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
         <v>135319562</v>
       </c>
       <c r="B34" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>623499</v>
       </c>
       <c r="R34" t="n">
-        <v>7307488</v>
+        <v>7307487</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4468,7 +4468,7 @@
         <v>135331027</v>
       </c>
       <c r="B35" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>135331029</v>
       </c>
       <c r="B36" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>135331130</v>
       </c>
       <c r="B37" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>135331350</v>
       </c>
       <c r="B38" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>135331670</v>
       </c>
       <c r="B39" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         <v>135333184</v>
       </c>
       <c r="B40" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
         <v>135333188</v>
       </c>
       <c r="B41" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>135333190</v>
       </c>
       <c r="B42" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         <v>135320009</v>
       </c>
       <c r="B43" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         <v>135331033</v>
       </c>
       <c r="B44" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>135333364</v>
       </c>
       <c r="B45" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         <v>135333375</v>
       </c>
       <c r="B46" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>135358216</v>
       </c>
       <c r="B47" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         <v>135332772</v>
       </c>
       <c r="B48" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
         <v>135332775</v>
       </c>
       <c r="B49" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6178,7 +6178,7 @@
         <v>135333183</v>
       </c>
       <c r="B50" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         <v>135319971</v>
       </c>
       <c r="B51" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>135331035</v>
       </c>
       <c r="B52" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>135332771</v>
       </c>
       <c r="B53" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6628,7 +6628,7 @@
         <v>135332776</v>
       </c>
       <c r="B54" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>135333181</v>
       </c>
       <c r="B55" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6860,7 +6860,7 @@
         <v>135333185</v>
       </c>
       <c r="B56" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         <v>135333191</v>
       </c>
       <c r="B57" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -10046,7 +10046,7 @@
         <v>135333372</v>
       </c>
       <c r="B83" t="n">
-        <v>99146</v>
+        <v>99173</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10167,7 +10167,7 @@
         <v>135337862</v>
       </c>
       <c r="B84" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10283,7 +10283,7 @@
         <v>135319835</v>
       </c>
       <c r="B85" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10395,7 +10395,7 @@
         <v>135331671</v>
       </c>
       <c r="B86" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
         <v>135331145</v>
       </c>
       <c r="B87" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>135331672</v>
       </c>
       <c r="B88" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10743,7 +10743,7 @@
         <v>135331673</v>
       </c>
       <c r="B89" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>135331674</v>
       </c>
       <c r="B90" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10975,7 +10975,7 @@
         <v>135331039</v>
       </c>
       <c r="B91" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11081,7 +11081,7 @@
         <v>135331124</v>
       </c>
       <c r="B92" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11197,7 +11197,7 @@
         <v>135331125</v>
       </c>
       <c r="B93" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11318,7 +11318,7 @@
         <v>135331126</v>
       </c>
       <c r="B94" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11434,7 +11434,7 @@
         <v>135331128</v>
       </c>
       <c r="B95" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11550,7 +11550,7 @@
         <v>135333186</v>
       </c>
       <c r="B96" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11666,7 +11666,7 @@
         <v>135331119</v>
       </c>
       <c r="B97" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>135331669</v>
       </c>
       <c r="B98" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11899,7 +11899,7 @@
         <v>135332778</v>
       </c>
       <c r="B99" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12015,7 +12015,7 @@
         <v>135333180</v>
       </c>
       <c r="B100" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12131,7 +12131,7 @@
         <v>135333382</v>
       </c>
       <c r="B101" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 64809-2023 artfynd.xlsx
+++ b/artfynd/A 64809-2023 artfynd.xlsx
@@ -1260,7 +1260,7 @@
         <v>135331133</v>
       </c>
       <c r="B7" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>135331136</v>
       </c>
       <c r="B8" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>135333192</v>
       </c>
       <c r="B9" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>135333193</v>
       </c>
       <c r="B11" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>135333379</v>
       </c>
       <c r="B12" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>135337856</v>
       </c>
       <c r="B13" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>135331031</v>
       </c>
       <c r="B15" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>135333195</v>
       </c>
       <c r="B16" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>135337861</v>
       </c>
       <c r="B17" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>135331135</v>
       </c>
       <c r="B26" t="n">
-        <v>92241</v>
+        <v>92243</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>135331140</v>
       </c>
       <c r="B27" t="n">
-        <v>92241</v>
+        <v>92243</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>135331131</v>
       </c>
       <c r="B28" t="n">
-        <v>96754</v>
+        <v>96756</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>135331132</v>
       </c>
       <c r="B29" t="n">
-        <v>97384</v>
+        <v>97386</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         <v>135331123</v>
       </c>
       <c r="B30" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
         <v>135320627</v>
       </c>
       <c r="B31" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>135332769</v>
       </c>
       <c r="B32" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>623499</v>
       </c>
       <c r="R34" t="n">
-        <v>7307488</v>
+        <v>7307487</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -10046,7 +10046,7 @@
         <v>135333372</v>
       </c>
       <c r="B83" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10167,7 +10167,7 @@
         <v>135337862</v>
       </c>
       <c r="B84" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10283,7 +10283,7 @@
         <v>135319835</v>
       </c>
       <c r="B85" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10395,7 +10395,7 @@
         <v>135331671</v>
       </c>
       <c r="B86" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
         <v>135331145</v>
       </c>
       <c r="B87" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>135331672</v>
       </c>
       <c r="B88" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10743,7 +10743,7 @@
         <v>135331673</v>
       </c>
       <c r="B89" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>135331674</v>
       </c>
       <c r="B90" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 64809-2023 artfynd.xlsx
+++ b/artfynd/A 64809-2023 artfynd.xlsx
@@ -4391,7 +4391,7 @@
         <v>623499</v>
       </c>
       <c r="R34" t="n">
-        <v>7307488</v>
+        <v>7307487</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
